--- a/countries/nz/2026-2029.xlsx
+++ b/countries/nz/2026-2029.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20814,7 +20814,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21606,7 +21606,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22398,7 +22398,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24378,7 +24378,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25170,7 +25170,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25566,7 +25566,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27150,7 +27150,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29922,7 +29922,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30318,7 +30318,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31506,7 +31506,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31902,7 +31902,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32298,7 +32298,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32694,7 +32694,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33090,7 +33090,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33486,7 +33486,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34278,7 +34278,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35070,7 +35070,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35466,7 +35466,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35862,7 +35862,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36258,7 +36258,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36405,9 +36405,6 @@
       <c r="O182" t="n">
         <v>764</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>14.44922996384477</v>
       </c>
@@ -36654,7 +36651,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36801,9 +36798,6 @@
       <c r="O184" t="n">
         <v>3</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.05673781399415487</v>
       </c>
@@ -37050,7 +37044,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37197,9 +37191,6 @@
       <c r="O186" t="n">
         <v>5</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.09456302332359146</v>
       </c>
@@ -37446,7 +37437,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37593,9 +37584,6 @@
       <c r="O188" t="n">
         <v>5</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.09456302332359146</v>
       </c>
@@ -37842,7 +37830,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37989,9 +37977,6 @@
       <c r="O190" t="n">
         <v>2</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -38238,7 +38223,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38385,9 +38370,6 @@
       <c r="O192" t="n">
         <v>36</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.6808537679298584</v>
       </c>
@@ -38634,7 +38616,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -38781,9 +38763,6 @@
       <c r="O194" t="n">
         <v>35</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.6619411632651402</v>
       </c>
@@ -39030,7 +39009,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39177,9 +39156,6 @@
       <c r="O196" t="n">
         <v>110</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>2.080386513119012</v>
       </c>
@@ -39426,7 +39402,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39573,9 +39549,6 @@
       <c r="O198" t="n">
         <v>8</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.1513008373177463</v>
       </c>
@@ -39822,7 +39795,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39969,9 +39942,6 @@
       <c r="O200" t="n">
         <v>6</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1134756279883097</v>
       </c>
@@ -40218,7 +40188,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40365,9 +40335,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -40614,7 +40581,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -40761,9 +40728,6 @@
       <c r="O204" t="n">
         <v>1</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -41010,7 +40974,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41157,9 +41121,6 @@
       <c r="O206" t="n">
         <v>343</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>6.487023399998373</v>
       </c>
@@ -41406,7 +41367,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41553,9 +41514,6 @@
       <c r="O208" t="n">
         <v>38</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.7186789772592951</v>
       </c>
@@ -41802,7 +41760,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41949,9 +41907,6 @@
       <c r="O210" t="n">
         <v>67</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>1.267144512536125</v>
       </c>
@@ -42198,7 +42153,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42345,9 +42300,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -42594,7 +42546,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42741,9 +42693,6 @@
       <c r="O214" t="n">
         <v>7</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.132388232653028</v>
       </c>
@@ -42990,7 +42939,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43137,9 +43086,6 @@
       <c r="O216" t="n">
         <v>37</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.6997663725945767</v>
       </c>
@@ -43386,7 +43332,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43533,9 +43479,6 @@
       <c r="O218" t="n">
         <v>13</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.2458638606413378</v>
       </c>
@@ -43782,7 +43725,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43929,9 +43872,6 @@
       <c r="O220" t="n">
         <v>2</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -44178,7 +44118,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44325,9 +44265,6 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -44574,7 +44511,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -44721,9 +44658,6 @@
       <c r="O224" t="n">
         <v>97</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>1.834522652477674</v>
       </c>
@@ -44970,7 +44904,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45117,9 +45051,6 @@
       <c r="O226" t="n">
         <v>87</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>1.645396605830491</v>
       </c>
@@ -45366,7 +45297,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45513,9 +45444,6 @@
       <c r="O228" t="n">
         <v>6</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.1134756279883097</v>
       </c>
@@ -45762,7 +45690,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45909,9 +45837,6 @@
       <c r="O230" t="n">
         <v>64</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>1.210406698541971</v>
       </c>
@@ -46158,7 +46083,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46305,9 +46230,6 @@
       <c r="O232" t="n">
         <v>33</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.6241159539357036</v>
       </c>
@@ -46554,7 +46476,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46701,9 +46623,6 @@
       <c r="O234" t="n">
         <v>45</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.8510672099123231</v>
       </c>
@@ -46950,7 +46869,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47097,9 +47016,6 @@
       <c r="O236" t="n">
         <v>24</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.4539025119532389</v>
       </c>
@@ -47346,7 +47262,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47493,9 +47409,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -47742,7 +47655,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -47889,9 +47802,6 @@
       <c r="O240" t="n">
         <v>4</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -48138,7 +48048,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -48285,9 +48195,6 @@
       <c r="O242" t="n">
         <v>834</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>15.77311229037505</v>
       </c>
@@ -48534,7 +48441,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -48681,9 +48588,6 @@
       <c r="O244" t="n">
         <v>4</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -48930,7 +48834,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -49077,9 +48981,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -49326,7 +49227,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49473,9 +49374,6 @@
       <c r="O248" t="n">
         <v>4</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -49722,7 +49620,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -49869,9 +49767,6 @@
       <c r="O250" t="n">
         <v>2</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -50118,7 +50013,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -50265,9 +50160,6 @@
       <c r="O252" t="n">
         <v>15</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.2836890699707744</v>
       </c>
@@ -50514,7 +50406,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -50661,9 +50553,6 @@
       <c r="O254" t="n">
         <v>32</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.6052033492709853</v>
       </c>
@@ -50910,7 +50799,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51057,9 +50946,6 @@
       <c r="O256" t="n">
         <v>194</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>3.669045304955348</v>
       </c>
@@ -51306,7 +51192,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51453,9 +51339,6 @@
       <c r="O258" t="n">
         <v>9</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.1702134419824646</v>
       </c>
@@ -51702,7 +51585,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -51849,9 +51732,6 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -52098,7 +51978,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52245,9 +52125,6 @@
       <c r="O262" t="n">
         <v>1</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -52494,7 +52371,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52641,9 +52518,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -52890,7 +52764,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53037,9 +52911,6 @@
       <c r="O266" t="n">
         <v>343</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>6.487023399998373</v>
       </c>
@@ -53286,7 +53157,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53433,9 +53304,6 @@
       <c r="O268" t="n">
         <v>40</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.7565041865887316</v>
       </c>
@@ -53682,7 +53550,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -53829,9 +53697,6 @@
       <c r="O270" t="n">
         <v>78</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>1.475183163848027</v>
       </c>
@@ -54078,7 +53943,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -54225,9 +54090,6 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
@@ -54474,7 +54336,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -54621,9 +54483,6 @@
       <c r="O274" t="n">
         <v>7</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.132388232653028</v>
       </c>
@@ -54870,7 +54729,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -55017,9 +54876,6 @@
       <c r="O276" t="n">
         <v>55</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>1.040193256559506</v>
       </c>
@@ -55266,7 +55122,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -55413,9 +55269,6 @@
       <c r="O278" t="n">
         <v>13</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.2458638606413378</v>
       </c>
@@ -55662,7 +55515,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -55809,9 +55662,6 @@
       <c r="O280" t="n">
         <v>2</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -56058,7 +55908,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -56205,9 +56055,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
@@ -56454,7 +56301,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -56601,9 +56448,6 @@
       <c r="O284" t="n">
         <v>85</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>1.607571396501055</v>
       </c>
@@ -56850,7 +56694,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -56997,9 +56841,6 @@
       <c r="O286" t="n">
         <v>78</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>1.475183163848027</v>
       </c>
@@ -57246,7 +57087,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -57393,9 +57234,6 @@
       <c r="O288" t="n">
         <v>2</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -57642,7 +57480,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -57789,9 +57627,6 @@
       <c r="O290" t="n">
         <v>84</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>1.588658791836336</v>
       </c>
@@ -58038,7 +57873,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -58185,9 +58020,6 @@
       <c r="O292" t="n">
         <v>27</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.5106403259473938</v>
       </c>
@@ -58434,7 +58266,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58581,9 +58413,6 @@
       <c r="O294" t="n">
         <v>48</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.9078050239064779</v>
       </c>
@@ -58830,7 +58659,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -58977,9 +58806,6 @@
       <c r="O296" t="n">
         <v>18</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.3404268839649292</v>
       </c>
@@ -59226,7 +59052,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59373,9 +59199,6 @@
       <c r="O298" t="n">
         <v>0</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0</v>
       </c>
@@ -59622,7 +59445,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -59769,9 +59592,6 @@
       <c r="O300" t="n">
         <v>3</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0.05673781399415487</v>
       </c>
@@ -60018,7 +59838,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -60165,9 +59985,6 @@
       <c r="O302" t="n">
         <v>611</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>11.55560145014288</v>
       </c>
@@ -60414,7 +60231,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -60561,9 +60378,6 @@
       <c r="O304" t="n">
         <v>3</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0.05673781399415487</v>
       </c>
@@ -60810,7 +60624,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -60957,9 +60771,6 @@
       <c r="O306" t="n">
         <v>4</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -61206,7 +61017,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -61353,9 +61164,6 @@
       <c r="O308" t="n">
         <v>10</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.1891260466471829</v>
       </c>
@@ -61602,7 +61410,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -61749,9 +61557,6 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0</v>
       </c>
@@ -61998,7 +61803,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -62145,9 +61950,6 @@
       <c r="O312" t="n">
         <v>11</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.2080386513119012</v>
       </c>
@@ -62394,7 +62196,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -62541,9 +62343,6 @@
       <c r="O314" t="n">
         <v>43</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0.8132420005828864</v>
       </c>
@@ -62790,7 +62589,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -62937,9 +62736,6 @@
       <c r="O316" t="n">
         <v>164</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>3.101667165013799</v>
       </c>
@@ -63186,7 +62982,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -63333,9 +63129,6 @@
       <c r="O318" t="n">
         <v>15</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.2836890699707744</v>
       </c>
@@ -63582,7 +63375,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -63729,9 +63522,6 @@
       <c r="O320" t="n">
         <v>2</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -63978,7 +63768,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -64125,9 +63915,6 @@
       <c r="O322" t="n">
         <v>2</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -64374,7 +64161,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -64521,9 +64308,6 @@
       <c r="O324" t="n">
         <v>1</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -64770,7 +64554,7 @@
       </c>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN325" t="b">
@@ -64917,9 +64701,6 @@
       <c r="O326" t="n">
         <v>333</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>6.297897353351191</v>
       </c>
@@ -65166,7 +64947,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -65313,9 +65094,6 @@
       <c r="O328" t="n">
         <v>36</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0.6808537679298584</v>
       </c>
@@ -65562,7 +65340,7 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN329" t="b">
@@ -65709,9 +65487,6 @@
       <c r="O330" t="n">
         <v>48</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.9078050239064779</v>
       </c>
@@ -65958,7 +65733,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -66105,9 +65880,6 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
@@ -66354,7 +66126,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -66501,9 +66273,6 @@
       <c r="O334" t="n">
         <v>7</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.132388232653028</v>
       </c>
@@ -66750,7 +66519,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -66897,9 +66666,6 @@
       <c r="O336" t="n">
         <v>68</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>1.286057117200844</v>
       </c>
@@ -67146,7 +66912,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -67293,9 +67059,6 @@
       <c r="O338" t="n">
         <v>7</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0.132388232653028</v>
       </c>
@@ -67542,7 +67305,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -67689,9 +67452,6 @@
       <c r="O340" t="n">
         <v>5</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.09456302332359146</v>
       </c>
@@ -67938,7 +67698,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN341" t="b">
@@ -68085,9 +67845,6 @@
       <c r="O342" t="n">
         <v>3</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0.05673781399415487</v>
       </c>
@@ -68334,7 +68091,7 @@
       </c>
       <c r="AM343" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN343" t="b">
@@ -68481,9 +68238,6 @@
       <c r="O344" t="n">
         <v>72</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>1.361707535859717</v>
       </c>
@@ -68730,7 +68484,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN345" t="b">
@@ -68877,9 +68631,6 @@
       <c r="O346" t="n">
         <v>53</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>1.002368047230069</v>
       </c>
@@ -69126,7 +68877,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -69273,9 +69024,6 @@
       <c r="O348" t="n">
         <v>4</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -69522,7 +69270,7 @@
       </c>
       <c r="AM349" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN349" t="b">
@@ -69669,9 +69417,6 @@
       <c r="O350" t="n">
         <v>91</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>1.721047024489364</v>
       </c>
@@ -69918,7 +69663,7 @@
       </c>
       <c r="AM351" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN351" t="b">
@@ -70065,9 +69810,6 @@
       <c r="O352" t="n">
         <v>35</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.6619411632651402</v>
       </c>
@@ -70314,7 +70056,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -70461,9 +70203,6 @@
       <c r="O354" t="n">
         <v>48</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0.9078050239064779</v>
       </c>
@@ -70710,7 +70449,7 @@
       </c>
       <c r="AM355" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN355" t="b">
@@ -70857,9 +70596,6 @@
       <c r="O356" t="n">
         <v>28</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0.5295529306121122</v>
       </c>
@@ -71106,7 +70842,7 @@
       </c>
       <c r="AM357" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN357" t="b">
@@ -71253,9 +70989,6 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0</v>
       </c>
@@ -71502,7 +71235,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN359" t="b">
@@ -71649,9 +71382,6 @@
       <c r="O360" t="n">
         <v>1</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -71898,7 +71628,7 @@
       </c>
       <c r="AM361" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN361" t="b">
